--- a/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
+++ b/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AD0339-A959-4DAF-AE05-7F564F3AC0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E792E0A-1458-42C5-B3D8-3C28B80438B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -21,17 +21,28 @@
     <sheet name="AddContact" sheetId="3" r:id="rId6"/>
     <sheet name="Contact" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
   <si>
     <t>Client</t>
   </si>
@@ -201,15 +212,9 @@
     <t>CompanyName</t>
   </si>
   <si>
-    <t>FirstName</t>
-  </si>
-  <si>
     <t>LastName</t>
   </si>
   <si>
-    <t>Emre</t>
-  </si>
-  <si>
     <t>Abale</t>
   </si>
   <si>
@@ -267,10 +272,6 @@
     <t>Rob Oudman</t>
   </si>
   <si>
-    <t xml:space="preserve"> 
-Debt Capital Markets</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -335,6 +336,21 @@
   </si>
   <si>
     <t>NY</t>
+  </si>
+  <si>
+    <t>Dpt</t>
+  </si>
+  <si>
+    <t>Emre Abale</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Debt Capital Markets</t>
+  </si>
+  <si>
+    <t>No Restrictions</t>
   </si>
 </sst>
 </file>
@@ -692,49 +708,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>84</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -749,12 +784,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -772,32 +807,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -831,6 +866,7 @@
     <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -920,13 +956,13 @@
         <v>43</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -937,10 +973,10 @@
         <v>53</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -961,7 +997,7 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L2" t="s">
         <v>52</v>
@@ -970,16 +1006,16 @@
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R2" t="s">
         <v>24</v>
@@ -988,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="U2" t="s">
         <v>27</v>
@@ -1003,19 +1039,19 @@
         <v>32</v>
       </c>
       <c r="Y2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Z2" t="s">
         <v>39</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AC2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AD2" t="s">
         <v>8</v>
@@ -1024,7 +1060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1032,10 +1068,10 @@
         <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1056,7 +1092,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -1065,16 +1101,16 @@
         <v>16</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R3" t="s">
         <v>24</v>
@@ -1083,7 +1119,7 @@
         <v>24</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="U3" t="s">
         <v>27</v>
@@ -1104,10 +1140,10 @@
         <v>39</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD3" t="s">
         <v>8</v>
@@ -1124,7 +1160,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1145,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s">
         <v>52</v>
@@ -1154,16 +1190,16 @@
         <v>16</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R4" t="s">
         <v>24</v>
@@ -1172,7 +1208,7 @@
         <v>24</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="U4" t="s">
         <v>27</v>
@@ -1187,16 +1223,19 @@
         <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Z4" t="s">
         <v>39</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>102</v>
       </c>
       <c r="AD4" t="s">
         <v>8</v>
@@ -1221,10 +1260,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -1238,19 +1277,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1375,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1345,21 +1384,21 @@
         <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
+++ b/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E792E0A-1458-42C5-B3D8-3C28B80438B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5CC46C-2499-4A36-B333-6EC2C7752ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>

--- a/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
+++ b/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5CC46C-2499-4A36-B333-6EC2C7752ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2156642-16CE-4886-A64B-9BEDDAA0E3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
   <si>
     <t>Client</t>
   </si>
@@ -1145,7 +1145,13 @@
       <c r="AB3" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="AC3" t="s">
+        <v>73</v>
+      </c>
       <c r="AD3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1238,6 +1244,9 @@
         <v>102</v>
       </c>
       <c r="AD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE4" t="s">
         <v>8</v>
       </c>
     </row>

--- a/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
+++ b/TestData/LV_TS04AndTS07_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2156642-16CE-4886-A64B-9BEDDAA0E3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB9D140-AC8B-4139-85C8-B24AD6E5D412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -293,9 +293,6 @@
     <t>Gemma Hardy</t>
   </si>
   <si>
-    <t>Indrajeet Singh</t>
-  </si>
-  <si>
     <t>Dimitri Drone</t>
   </si>
   <si>
@@ -351,6 +348,9 @@
   </si>
   <si>
     <t>No Restrictions</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
   </si>
 </sst>
 </file>
@@ -727,18 +727,18 @@
         <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
         <v>86</v>
       </c>
-      <c r="B2" t="s">
-        <v>87</v>
-      </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
         <v>69</v>
@@ -752,7 +752,7 @@
         <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
         <v>44</v>
@@ -760,13 +760,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" t="s">
-        <v>85</v>
-      </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
         <v>66</v>
@@ -784,12 +784,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -807,32 +807,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -997,7 +997,7 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L2" t="s">
         <v>52</v>
@@ -1068,10 +1068,10 @@
         <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1092,7 +1092,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -1166,7 +1166,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1187,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s">
         <v>52</v>
@@ -1241,7 +1241,7 @@
         <v>77</v>
       </c>
       <c r="AC4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AD4" t="s">
         <v>8</v>
@@ -1393,7 +1393,7 @@
         <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>56</v>
@@ -1404,7 +1404,7 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>57</v>
